--- a/forms/trg/Formulir_TRG_invaquatic.xlsx
+++ b/forms/trg/Formulir_TRG_invaquatic.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,12 +937,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Andi Iqbal Burhanuddin, S.T., M.Fish.Sc., Ph.D.</t>
+          <t>Prof. Dr. Ir. Budimawan, DEA.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -950,7 +950,11 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Fish Biology || Fisheries || Coastal Resorces Management || life environement</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -970,12 +974,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Irmawati, S.Pi, M.Si.</t>
+          <t>Prof. Andi Iqbal Burhanuddin, S.T., M.Fish.Sc., Ph.D.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1003,12 +1007,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Andi Haerul, S.Kel., M.Si</t>
+          <t>Dr. Irmawati, S.Pi, M.Si.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1036,12 +1040,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Andi Annisar Dzati Iffah, S.Kel., M.Si</t>
+          <t>Andi Haerul, S.Kel., M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1069,15 +1073,19 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Nathalie NIQUIL, Ph.D</t>
+          <t>Andi Annisar Dzati Iffah, S.Kel., M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
@@ -1098,19 +1106,15 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nurjirana, S.Kel</t>
+          <t>Prof. Nathalie NIQUIL, Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
@@ -1131,12 +1135,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Afrisal, S.Kel</t>
+          <t>Dr. Nurjirana, S.Kel</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1164,12 +1168,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Haerunnisa, S.Pi., M.Si.</t>
+          <t>Dr. Muhammad Afrisal, S.Kel</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1197,12 +1201,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Marwah</t>
+          <t>Dr. Haerunnisa, S.Pi., M.Si.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1230,12 +1234,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ardyansyah Kahar</t>
+          <t>Marwah</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1261,10 +1265,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Ardyansyah Kahar</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>INVAQUATIC is a research group focused on managing aquatic invasive alien species across freshwater, coastal, and marine ecosystems. We integrate ecology, genetics, and monitoring to support biodiversity conservation, ecosystem resilience, and sustainable fisheries, while advancing science-based solutions, policy development, and global collaboration to address environmental challenges driven by human activities and climate change.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1272,7 +1292,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1461,15 +1485,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
